--- a/data/downloads/EGl7zfkXhhK2ODm4ucrKx6xK.xlsx
+++ b/data/downloads/EGl7zfkXhhK2ODm4ucrKx6xK.xlsx
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>Overall PASC (Long COVID) prevalence identified via AI phenotyping (P2RC) among COVID-19 patients across 4 US regions (2020-2024): the document reports 16.28% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 27 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is below every survey wave interval in that period. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
+          <t>Overall PASC (Long COVID) prevalence identified via AI phenotyping (P2RC) among COVID-19 patients across 4 US regions (2020-2024): the document reports 16.28% as the share of adults who ever had COVID-19 that ever experienced Long COVID; the national survey's 27 wave(s) in that period ranged from 25.6% to 35.1% (interval bounds 24.9% to 36%), so the document's figure is below every survey wave interval in that period. The survey is self-reported adults; a different definition or population in the document makes a gap expected, so treat it as a prompt to check. The survey has no data for 2020, 2021. Federal source: household survey (self-report), 2022-2024; computed in code from the federal file; no AI model.</t>
         </is>
       </c>
     </row>
